--- a/leçon.xlsx
+++ b/leçon.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ff63f536390cb2c5/Bureau/oulpan-quizz/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="435" documentId="8_{BC024BC0-46C4-4E8F-9CE8-AFE3D1C5A028}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EA908020-8B44-44FB-9791-7A4C1092DD68}"/>
+  <xr:revisionPtr revIDLastSave="744" documentId="8_{BC024BC0-46C4-4E8F-9CE8-AFE3D1C5A028}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8D39B440-ACC5-46B0-B8CB-482849EBE409}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{5D5EA3D2-9A17-4210-BC2E-7FDF26C4E938}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="4" activeTab="7" xr2:uid="{5D5EA3D2-9A17-4210-BC2E-7FDF26C4E938}"/>
   </bookViews>
   <sheets>
     <sheet name="של־" sheetId="7" r:id="rId1"/>
@@ -20,6 +20,9 @@
     <sheet name="verbe+ על־" sheetId="3" r:id="rId5"/>
     <sheet name="verbe +עם" sheetId="4" r:id="rId6"/>
     <sheet name="verbe +את" sheetId="6" r:id="rId7"/>
+    <sheet name="Verbe + ב־" sheetId="8" r:id="rId8"/>
+    <sheet name="Verbe + בשביל" sheetId="9" r:id="rId9"/>
+    <sheet name="Verbe + אצל" sheetId="10" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -45,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="340">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="651" uniqueCount="471">
   <si>
     <t>regle</t>
   </si>
@@ -2076,12 +2079,6 @@
     <t>ממך (miMKHA)</t>
   </si>
   <si>
-    <t>ממך(mimakh)</t>
-  </si>
-  <si>
-    <t>ממנו (miMÉnou )</t>
-  </si>
-  <si>
     <t>ממנה (miMÉna)</t>
   </si>
   <si>
@@ -2600,13 +2597,516 @@
       </rPr>
       <t>ממך</t>
     </r>
+  </si>
+  <si>
+    <t>ממנו (miMÉno )</t>
+  </si>
+  <si>
+    <t>ממך(mimekh)</t>
+  </si>
+  <si>
+    <t>1. ב־ (dans, en, à)</t>
+  </si>
+  <si>
+    <t>Règle</t>
+  </si>
+  <si>
+    <t>Verbe + ב־</t>
+  </si>
+  <si>
+    <t>LIEU → ב־ (dans, en, à)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">L'action se déroule </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>à l'intérieur d'un lieu</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ou </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>dans un endroit</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>→ localisation</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">→ </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Où ?</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> → verbe + </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ב־</t>
+    </r>
+  </si>
+  <si>
+    <t>être dans</t>
+  </si>
+  <si>
+    <t>habiter dans</t>
+  </si>
+  <si>
+    <t>travailler dans</t>
+  </si>
+  <si>
+    <t>étudier dans</t>
+  </si>
+  <si>
+    <t>manger dans</t>
+  </si>
+  <si>
+    <t>בי (bi)</t>
+  </si>
+  <si>
+    <t>בך (bekha)</t>
+  </si>
+  <si>
+    <t>בך (bakh)</t>
+  </si>
+  <si>
+    <t>בו (bo)</t>
+  </si>
+  <si>
+    <t>בה (ba)</t>
+  </si>
+  <si>
+    <t>בנו (banou)</t>
+  </si>
+  <si>
+    <t>בכם (bakhem)</t>
+  </si>
+  <si>
+    <t>בכן (bakhen)</t>
+  </si>
+  <si>
+    <t>בהם (bahem)</t>
+  </si>
+  <si>
+    <t>בהן (bahen)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">verbes fréquents : </t>
+  </si>
+  <si>
+    <t>Verbe + בשביל</t>
+  </si>
+  <si>
+    <t>BUT / BÉNÉFICIAIRE → בשביל</t>
+  </si>
+  <si>
+    <t>faire pour</t>
+  </si>
+  <si>
+    <t>acheter pour</t>
+  </si>
+  <si>
+    <t>cuisiner pour</t>
+  </si>
+  <si>
+    <t>préparer pour</t>
+  </si>
+  <si>
+    <t>attendre pour</t>
+  </si>
+  <si>
+    <t>בשבילי (bishvili)</t>
+  </si>
+  <si>
+    <t>בשבילך (bishvilkha)</t>
+  </si>
+  <si>
+    <t>בשבילך (bishvilakh)</t>
+  </si>
+  <si>
+    <t>בשבילו (bishvilo)</t>
+  </si>
+  <si>
+    <t>בשבילה (bishvila)</t>
+  </si>
+  <si>
+    <t>בשבילנו (bishvilénou)</t>
+  </si>
+  <si>
+    <t>בשבילכם (bishvilkhem)</t>
+  </si>
+  <si>
+    <t>בשבילכן (bishvilkhen)</t>
+  </si>
+  <si>
+    <t>בשבילם (bishvilam)</t>
+  </si>
+  <si>
+    <t>בשבילן (bishvilan)</t>
+  </si>
+  <si>
+    <t>Je cuisine pour toi.</t>
+  </si>
+  <si>
+    <t>Elle achète un cadeau pour lui.</t>
+  </si>
+  <si>
+    <t>Nous préparons le repas pour les enfants.</t>
+  </si>
+  <si>
+    <t>Ils travaillent pour nous.</t>
+  </si>
+  <si>
+    <t>Ce café est pour toi.</t>
+  </si>
+  <si>
+    <t>J'ai fait cela pour vous.</t>
+  </si>
+  <si>
+    <t>Elle chante pour eux.</t>
+  </si>
+  <si>
+    <t>Nous attendons pour elle.</t>
+  </si>
+  <si>
+    <t>Tu écris une lettre pour moi.</t>
+  </si>
+  <si>
+    <t>Ils construisent une maison pour leurs parents.</t>
+  </si>
+  <si>
+    <t>L'action est faite pour quelqu'un.</t>
+  </si>
+  <si>
+    <t>→ bénéfice, → Pour qui ?</t>
+  </si>
+  <si>
+    <t>pour Moi</t>
+  </si>
+  <si>
+    <t>pour Toi (m.)</t>
+  </si>
+  <si>
+    <t>pour Toi (f.)</t>
+  </si>
+  <si>
+    <t>pour Lui</t>
+  </si>
+  <si>
+    <t>pour Elle</t>
+  </si>
+  <si>
+    <t>pour Nous</t>
+  </si>
+  <si>
+    <t>pour Vous (m.pl.)</t>
+  </si>
+  <si>
+    <t>pour Vous (f.pl.)</t>
+  </si>
+  <si>
+    <t>pour Eux</t>
+  </si>
+  <si>
+    <t>pour Elles</t>
+  </si>
+  <si>
+    <t>אני מבשל בשבילך</t>
+  </si>
+  <si>
+    <t>היא קונה מתנה בשבילו</t>
+  </si>
+  <si>
+    <t>אנחנו מכינים ארוחה בשביל הילדים</t>
+  </si>
+  <si>
+    <t>הם עובדים בשבילנו</t>
+  </si>
+  <si>
+    <t>הקפה הזה בשבילך</t>
+  </si>
+  <si>
+    <t>עשיתי את זה בשבילכם</t>
+  </si>
+  <si>
+    <t>היא שרה בשבילם</t>
+  </si>
+  <si>
+    <t>אנחנו מחכים בשבילה</t>
+  </si>
+  <si>
+    <t>אתה כותב מכתב בשבילי</t>
+  </si>
+  <si>
+    <t>הם בונים בית בשביל ההורים שלהם</t>
+  </si>
+  <si>
+    <t>Verbe + אצל</t>
+  </si>
+  <si>
+    <t>CHEZ QUELQU'UN → אצל</t>
+  </si>
+  <si>
+    <t>aller chez</t>
+  </si>
+  <si>
+    <t>être chez</t>
+  </si>
+  <si>
+    <t>dormir chez</t>
+  </si>
+  <si>
+    <t>manger chez</t>
+  </si>
+  <si>
+    <t>travailler chez (un employeur)</t>
+  </si>
+  <si>
+    <t>On indique qu'on est chez une personne ou dans son cabinet, bureau, maison...</t>
+  </si>
+  <si>
+    <t>→ chez quelqu'un, → → Chez qui ?</t>
+  </si>
+  <si>
+    <t>אצלי (etsli)</t>
+  </si>
+  <si>
+    <t>אצלך (etslekha)</t>
+  </si>
+  <si>
+    <t>אצלך (etslekh)</t>
+  </si>
+  <si>
+    <t>אצלו (etslo)</t>
+  </si>
+  <si>
+    <t>אצלה (etsla)</t>
+  </si>
+  <si>
+    <t>אצלנו (etslénou)</t>
+  </si>
+  <si>
+    <t>אצלכם (etslekhem)</t>
+  </si>
+  <si>
+    <t>אצלכן (etslekhen)</t>
+  </si>
+  <si>
+    <t>אצלם (etslam)</t>
+  </si>
+  <si>
+    <t>אצלן (etslan)</t>
+  </si>
+  <si>
+    <t>Je suis chez toi.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">אני </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>אצלך</t>
+    </r>
+  </si>
+  <si>
+    <t>Nous mangeons chez nos amis.</t>
+  </si>
+  <si>
+    <t>Elle dort chez sa mère.</t>
+  </si>
+  <si>
+    <t>Ils travaillent chez Microsoft.</t>
+  </si>
+  <si>
+    <t>Je vais chez le médecin.</t>
+  </si>
+  <si>
+    <t>Les enfants sont chez leurs grands-parents.</t>
+  </si>
+  <si>
+    <t>Elle reste chez nous.</t>
+  </si>
+  <si>
+    <t>Tu viens chez moi.</t>
+  </si>
+  <si>
+    <t>Nous habitons chez nos parents.</t>
+  </si>
+  <si>
+    <t>Le chat est chez le voisin.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">החתול </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>אצל השכן</t>
+    </r>
+  </si>
+  <si>
+    <t>אנחנו אוכלים אצל החברים שלנו</t>
+  </si>
+  <si>
+    <t>היא ישנה אצל אמא שלה</t>
+  </si>
+  <si>
+    <t>הם עובדים אצל מיקרוסופט</t>
+  </si>
+  <si>
+    <t>אני הולך אצל הרופא</t>
+  </si>
+  <si>
+    <t>הילדים אצל הסבא והסבתא שלהם</t>
+  </si>
+  <si>
+    <t>היא נשארת אצלנו</t>
+  </si>
+  <si>
+    <t>אתה בא אצלי</t>
+  </si>
+  <si>
+    <t>אנחנו גרים אצל ההורים שלנו</t>
+  </si>
+  <si>
+    <t>Je crois en moi.</t>
+  </si>
+  <si>
+    <t>אני מאמין בי.</t>
+  </si>
+  <si>
+    <t>Je crois en toi.</t>
+  </si>
+  <si>
+    <t>אני מאמין בך.</t>
+  </si>
+  <si>
+    <t>Elle croit en lui.</t>
+  </si>
+  <si>
+    <t>היא מאמינה בו.</t>
+  </si>
+  <si>
+    <t>Nous croyons en elle.</t>
+  </si>
+  <si>
+    <t>אנחנו מאמינים בה.</t>
+  </si>
+  <si>
+    <t>Ils croient en nous.</t>
+  </si>
+  <si>
+    <t>הם מאמינים בנו.</t>
+  </si>
+  <si>
+    <t>Je crois en vous.</t>
+  </si>
+  <si>
+    <t>אני מאמין בכם.</t>
+  </si>
+  <si>
+    <t>Elle croit en vous. (f.)</t>
+  </si>
+  <si>
+    <t>היא מאמינה בכן.</t>
+  </si>
+  <si>
+    <t>Nous croyons en eux.</t>
+  </si>
+  <si>
+    <t>אנחנו מאמינים בהם.</t>
+  </si>
+  <si>
+    <t>Je crois en elles.</t>
+  </si>
+  <si>
+    <t>אני מאמין בהן.</t>
+  </si>
+  <si>
+    <t>Le professeur croit en toi.</t>
+  </si>
+  <si>
+    <t>המורה מאמין בך.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2661,6 +3161,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -2703,7 +3211,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2740,6 +3248,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3100,30 +3611,30 @@
     </row>
     <row r="2" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C2" s="13" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="D2" s="13"/>
     </row>
     <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C3" s="13" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="D3" s="13"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="18" x14ac:dyDescent="0.25">
       <c r="C5" s="15" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="G5" s="5"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C6" s="5" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="G6" s="16"/>
     </row>
@@ -3176,7 +3687,7 @@
         <v>33</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="E13" t="s">
         <v>44</v>
@@ -3187,7 +3698,7 @@
         <v>34</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="E14" t="s">
         <v>44</v>
@@ -3209,7 +3720,7 @@
         <v>36</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="E16" t="s">
         <v>44</v>
@@ -3220,7 +3731,7 @@
         <v>37</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -3228,7 +3739,7 @@
         <v>38</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -3236,7 +3747,7 @@
         <v>39</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -3244,7 +3755,7 @@
         <v>40</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -3489,6 +4000,284 @@
       <c r="D53" s="4" t="s">
         <v>202</v>
       </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6594D8E9-483D-430C-B26C-2021A6908BAD}">
+  <dimension ref="A1:I38"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="56" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>412</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C2" t="s">
+        <v>419</v>
+      </c>
+      <c r="F2" s="4"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C3" t="s">
+        <v>420</v>
+      </c>
+      <c r="H3" s="4"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C4" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C5" s="5" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C6" s="5" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C7" s="5" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C8" s="5" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C9" s="5" t="s">
+        <v>418</v>
+      </c>
+      <c r="F9" s="5"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H10" s="5"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H11" s="5"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C14" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C15" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C16" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C17" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C18" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C19" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="24" x14ac:dyDescent="0.25">
+      <c r="C20" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="H20" s="17" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>44</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C22" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="H22" s="6"/>
+      <c r="I22" s="6"/>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C23" s="3"/>
+      <c r="D23" s="3"/>
+      <c r="H23" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>3</v>
+      </c>
+      <c r="C25" t="s">
+        <v>431</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>432</v>
+      </c>
+      <c r="H25" s="5"/>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C26" t="s">
+        <v>433</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>443</v>
+      </c>
+      <c r="H26" s="5"/>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C27" t="s">
+        <v>434</v>
+      </c>
+      <c r="D27" t="s">
+        <v>444</v>
+      </c>
+      <c r="H27" s="5"/>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C28" t="s">
+        <v>435</v>
+      </c>
+      <c r="D28" t="s">
+        <v>445</v>
+      </c>
+      <c r="H28" s="5"/>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C29" t="s">
+        <v>436</v>
+      </c>
+      <c r="D29" t="s">
+        <v>446</v>
+      </c>
+      <c r="H29" s="5"/>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C30" t="s">
+        <v>437</v>
+      </c>
+      <c r="D30" t="s">
+        <v>447</v>
+      </c>
+      <c r="H30" s="5"/>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C31" t="s">
+        <v>438</v>
+      </c>
+      <c r="D31" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C32" t="s">
+        <v>439</v>
+      </c>
+      <c r="D32" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="33" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C33" t="s">
+        <v>440</v>
+      </c>
+      <c r="D33" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="34" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C34" t="s">
+        <v>441</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="35" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C35" s="5"/>
+    </row>
+    <row r="38" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C38" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3772,52 +4561,50 @@
       <c r="C2" t="s">
         <v>2</v>
       </c>
-      <c r="G2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="C3" s="4" t="s">
         <v>29</v>
       </c>
+      <c r="G3" s="1" t="s">
+        <v>340</v>
+      </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C4" s="4" t="s">
-        <v>315</v>
-      </c>
-      <c r="G4" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="24" x14ac:dyDescent="0.25">
       <c r="C5" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="G5" s="5"/>
+      <c r="G5" s="17" t="s">
+        <v>341</v>
+      </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C6" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="G6" s="16" t="s">
-        <v>44</v>
-      </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C7" s="5" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+      <c r="G7" s="4" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C8" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="G8" s="15" t="s">
-        <v>44</v>
-      </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="G9" s="5"/>
+      <c r="G9" s="4" t="s">
+        <v>343</v>
+      </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
@@ -3827,10 +4614,7 @@
         <v>31</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>236</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>44</v>
+        <v>234</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -3838,7 +4622,10 @@
         <v>32</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>238</v>
+        <v>236</v>
+      </c>
+      <c r="G11" t="s">
+        <v>344</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -3846,7 +4633,7 @@
         <v>33</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -3854,7 +4641,10 @@
         <v>34</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>239</v>
+        <v>237</v>
+      </c>
+      <c r="G13" t="s">
+        <v>345</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -3862,7 +4652,7 @@
         <v>35</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -3870,7 +4660,10 @@
         <v>36</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>241</v>
+        <v>239</v>
+      </c>
+      <c r="G15" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -3878,34 +4671,54 @@
         <v>37</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+        <v>240</v>
+      </c>
+      <c r="G16" s="5"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C17" s="8" t="s">
         <v>38</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+        <v>241</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C18" s="8" t="s">
         <v>39</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+        <v>242</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C19" s="8" t="s">
         <v>40</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+        <v>243</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G20" s="5" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G21" s="5" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>3</v>
       </c>
@@ -3916,7 +4729,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C24" s="3" t="s">
         <v>6</v>
       </c>
@@ -3924,7 +4737,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="C25" s="3" t="s">
         <v>8</v>
       </c>
@@ -3932,7 +4745,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="C26" s="3" t="s">
         <v>10</v>
       </c>
@@ -3940,7 +4753,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="C27" s="3" t="s">
         <v>12</v>
       </c>
@@ -3948,7 +4761,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="C28" s="3" t="s">
         <v>14</v>
       </c>
@@ -3956,7 +4769,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="C29" s="3" t="s">
         <v>16</v>
       </c>
@@ -3964,7 +4777,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="C30" s="3" t="s">
         <v>18</v>
       </c>
@@ -3972,7 +4785,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="C31" s="3" t="s">
         <v>20</v>
       </c>
@@ -3980,7 +4793,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="C32" s="3" t="s">
         <v>22</v>
       </c>
@@ -4038,7 +4851,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -4065,7 +4878,7 @@
         <v>33</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>228</v>
+        <v>339</v>
       </c>
       <c r="E11" s="4"/>
     </row>
@@ -4074,7 +4887,7 @@
         <v>34</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>229</v>
+        <v>338</v>
       </c>
       <c r="E12" s="4"/>
     </row>
@@ -4083,7 +4896,7 @@
         <v>35</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -4091,7 +4904,7 @@
         <v>36</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="E14" s="4"/>
     </row>
@@ -4100,7 +4913,7 @@
         <v>37</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E15" s="4"/>
     </row>
@@ -4109,7 +4922,7 @@
         <v>38</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="E16" s="4"/>
     </row>
@@ -4118,7 +4931,7 @@
         <v>39</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E17" s="4"/>
     </row>
@@ -4127,7 +4940,7 @@
         <v>40</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E18" s="4"/>
     </row>
@@ -4142,10 +4955,10 @@
         <v>3</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>44</v>
@@ -4153,10 +4966,10 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C23" s="3" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>44</v>
@@ -4164,10 +4977,10 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C24" s="3" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>44</v>
@@ -4175,10 +4988,10 @@
     </row>
     <row r="25" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="C25" s="3" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>44</v>
@@ -4186,10 +4999,10 @@
     </row>
     <row r="26" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="C26" s="3" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>44</v>
@@ -4197,10 +5010,10 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C27" s="3" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>44</v>
@@ -4208,10 +5021,10 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C28" s="3" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>44</v>
@@ -4219,10 +5032,10 @@
     </row>
     <row r="29" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="C29" s="3" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>44</v>
@@ -4230,10 +5043,10 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C30" s="3" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>44</v>
@@ -4241,10 +5054,10 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C31" s="3" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>44</v>
@@ -4342,45 +5155,45 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C5" s="5" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C6" s="16" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C7" s="16" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C8" s="16" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C9" s="16" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="G9" s="16"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C10" s="16" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="G10" s="16"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C11" s="5" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="G11" s="16"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C12" s="5" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="G12" s="16"/>
     </row>
@@ -4393,10 +5206,10 @@
         <v>30</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="G15" t="s">
         <v>44</v>
@@ -4404,10 +5217,10 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C16" s="3" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="G16" s="6" t="s">
         <v>44</v>
@@ -4418,10 +5231,10 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C17" s="3" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="G17" s="7" t="s">
         <v>44</v>
@@ -4430,10 +5243,10 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C18" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="G18" s="7" t="s">
         <v>44</v>
@@ -4442,10 +5255,10 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C19" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="G19" s="7" t="s">
         <v>44</v>
@@ -4454,10 +5267,10 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C20" s="3" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G20" s="7" t="s">
         <v>44</v>
@@ -4466,10 +5279,10 @@
     </row>
     <row r="21" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="C21" s="3" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="G21" s="7" t="s">
         <v>44</v>
@@ -4478,10 +5291,10 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C22" s="3" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="G22" s="7" t="s">
         <v>44</v>
@@ -4490,10 +5303,10 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C23" s="3" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="G23" s="7" t="s">
         <v>44</v>
@@ -4504,10 +5317,10 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C24" s="3" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="G24" s="7" t="s">
         <v>44</v>
@@ -4546,10 +5359,10 @@
         <v>3</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
@@ -4637,111 +5450,111 @@
         <v>49</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="40" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C40" s="3" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="41" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C41" s="3" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="42" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C42" s="3" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="43" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C43" s="3" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="44" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C44" s="3" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="46" spans="3:4" ht="30" x14ac:dyDescent="0.25">
       <c r="C46" s="3" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="47" spans="3:4" ht="30" x14ac:dyDescent="0.25">
       <c r="C47" s="3" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="D47" s="7" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="48" spans="3:4" ht="30" x14ac:dyDescent="0.25">
       <c r="C48" s="3" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="49" spans="3:4" ht="30" x14ac:dyDescent="0.25">
       <c r="C49" s="3" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D49" s="7" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="50" spans="3:4" ht="30" x14ac:dyDescent="0.25">
       <c r="C50" s="3" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="51" spans="3:4" ht="30" x14ac:dyDescent="0.25">
       <c r="C51" s="3" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="52" spans="3:4" ht="30" x14ac:dyDescent="0.25">
       <c r="C52" s="3" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="D52" s="7" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="53" spans="3:4" ht="30" x14ac:dyDescent="0.25">
       <c r="C53" s="3" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="D53" s="7" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
   </sheetData>
@@ -4779,17 +5592,17 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C5" s="16" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="18" x14ac:dyDescent="0.25">
       <c r="C6" s="15" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -4799,7 +5612,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="F8" s="5"/>
     </row>
@@ -5187,4 +6000,540 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6D4A1BD-20D7-40FF-93B7-1436AFCA719F}">
+  <dimension ref="A1:G37"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="34.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>342</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C2" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C3" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C4" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C5" s="5" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C6" s="5" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C7" s="5" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C8" s="5" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C9" s="5" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C13" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C14" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C15" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C16" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C17" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C18" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C19" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>44</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C21" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C23" s="3"/>
+      <c r="D23" s="3"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>3</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C25" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C26" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C27" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C28" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C29" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C30" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C31" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C32" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="33" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C33" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="37" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C37" s="5"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8B16424-2FD7-4630-9E72-FF4204C3C3BB}">
+  <dimension ref="A1:I45"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="56" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>363</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C2" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C3" t="s">
+        <v>391</v>
+      </c>
+      <c r="H3" s="4"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C4" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C5" s="5" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C6" s="5" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C7" s="5" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C8" s="5" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C9" s="5" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H10" s="5"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H11" s="5"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C14" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C15" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C16" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C17" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C18" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C19" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="24" x14ac:dyDescent="0.25">
+      <c r="C20" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="H20" s="17" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>44</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C22" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="H22" s="6"/>
+      <c r="I22" s="6"/>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C23" s="3"/>
+      <c r="D23" s="3"/>
+      <c r="H23" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>3</v>
+      </c>
+      <c r="C25" t="s">
+        <v>380</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>402</v>
+      </c>
+      <c r="H25" s="5"/>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C26" t="s">
+        <v>381</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>403</v>
+      </c>
+      <c r="H26" s="5"/>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C27" t="s">
+        <v>382</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C28" t="s">
+        <v>383</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C29" t="s">
+        <v>384</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>406</v>
+      </c>
+      <c r="H29" s="5"/>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C30" t="s">
+        <v>385</v>
+      </c>
+      <c r="D30" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C31" t="s">
+        <v>386</v>
+      </c>
+      <c r="D31" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C32" t="s">
+        <v>387</v>
+      </c>
+      <c r="D32" t="s">
+        <v>409</v>
+      </c>
+      <c r="H32" s="5"/>
+    </row>
+    <row r="33" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C33" t="s">
+        <v>388</v>
+      </c>
+      <c r="D33" t="s">
+        <v>410</v>
+      </c>
+      <c r="H33" s="5"/>
+    </row>
+    <row r="34" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C34" t="s">
+        <v>389</v>
+      </c>
+      <c r="D34" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="36" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="H36" s="5"/>
+    </row>
+    <row r="37" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="H37" s="5"/>
+    </row>
+    <row r="40" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="H40" s="5"/>
+    </row>
+    <row r="41" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="H41" s="5"/>
+    </row>
+    <row r="44" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="H44" s="5"/>
+    </row>
+    <row r="45" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="H45" s="5"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/leçon.xlsx
+++ b/leçon.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ff63f536390cb2c5/Bureau/oulpan-quizz/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="744" documentId="8_{BC024BC0-46C4-4E8F-9CE8-AFE3D1C5A028}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8D39B440-ACC5-46B0-B8CB-482849EBE409}"/>
+  <xr:revisionPtr revIDLastSave="793" documentId="8_{BC024BC0-46C4-4E8F-9CE8-AFE3D1C5A028}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C9AB88A6-4E4F-434F-97A0-25D44372D542}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="4" activeTab="7" xr2:uid="{5D5EA3D2-9A17-4210-BC2E-7FDF26C4E938}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{5D5EA3D2-9A17-4210-BC2E-7FDF26C4E938}"/>
   </bookViews>
   <sheets>
     <sheet name="של־" sheetId="7" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="651" uniqueCount="471">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="651" uniqueCount="520">
   <si>
     <t>regle</t>
   </si>
@@ -3100,6 +3100,153 @@
   </si>
   <si>
     <t>המורה מאמין בך.</t>
+  </si>
+  <si>
+    <t>en Moi</t>
+  </si>
+  <si>
+    <t>en Toi (m.)</t>
+  </si>
+  <si>
+    <t>en Toi (f.)</t>
+  </si>
+  <si>
+    <t>en Lui</t>
+  </si>
+  <si>
+    <t>en Elle</t>
+  </si>
+  <si>
+    <t>en Nous</t>
+  </si>
+  <si>
+    <t>en Vous (m.pl.)</t>
+  </si>
+  <si>
+    <t>en Vous (f.pl.)</t>
+  </si>
+  <si>
+    <t>en Eux</t>
+  </si>
+  <si>
+    <t>en Elles</t>
+  </si>
+  <si>
+    <t>chez Moi</t>
+  </si>
+  <si>
+    <t>chez Toi (m.)</t>
+  </si>
+  <si>
+    <t>chez Toi (f.)</t>
+  </si>
+  <si>
+    <t>chez Lui</t>
+  </si>
+  <si>
+    <t>chez Elle</t>
+  </si>
+  <si>
+    <t>chez Nous</t>
+  </si>
+  <si>
+    <t>chez Vous (m.pl.)</t>
+  </si>
+  <si>
+    <t>chez Vous (f.pl.)</t>
+  </si>
+  <si>
+    <t>chez Eux</t>
+  </si>
+  <si>
+    <t>chez Elles</t>
+  </si>
+  <si>
+    <t>de Toi (m.)</t>
+  </si>
+  <si>
+    <t>de Toi (f.)</t>
+  </si>
+  <si>
+    <t>de Lui</t>
+  </si>
+  <si>
+    <t>de Elle</t>
+  </si>
+  <si>
+    <t>de Nous</t>
+  </si>
+  <si>
+    <t>de Vous (m.pl.)</t>
+  </si>
+  <si>
+    <t>de Vous (f.pl.)</t>
+  </si>
+  <si>
+    <t>de Eux</t>
+  </si>
+  <si>
+    <t>de Elles</t>
+  </si>
+  <si>
+    <t>à Moi</t>
+  </si>
+  <si>
+    <t>à Toi (m.)</t>
+  </si>
+  <si>
+    <t>à Toi (f.)</t>
+  </si>
+  <si>
+    <t>à Lui</t>
+  </si>
+  <si>
+    <t>à Elle</t>
+  </si>
+  <si>
+    <t>à Nous</t>
+  </si>
+  <si>
+    <t>à Vous (m.pl.)</t>
+  </si>
+  <si>
+    <t>à Vous (f.pl.)</t>
+  </si>
+  <si>
+    <t>à Eux</t>
+  </si>
+  <si>
+    <t>à Elles</t>
+  </si>
+  <si>
+    <t>Mon</t>
+  </si>
+  <si>
+    <t>Ton(m.)</t>
+  </si>
+  <si>
+    <t>Ton(f.)</t>
+  </si>
+  <si>
+    <t>son</t>
+  </si>
+  <si>
+    <t>sa</t>
+  </si>
+  <si>
+    <t>Notre</t>
+  </si>
+  <si>
+    <t>Votre (m.pl.)</t>
+  </si>
+  <si>
+    <t>Votre(f.pl.)</t>
+  </si>
+  <si>
+    <t>leurs (m,pl)</t>
+  </si>
+  <si>
+    <t>leurs (f,pl)</t>
   </si>
 </sst>
 </file>
@@ -3662,7 +3809,7 @@
         <v>30</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>31</v>
+        <v>510</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>224</v>
@@ -3673,7 +3820,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C12" s="8" t="s">
-        <v>32</v>
+        <v>511</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>225</v>
@@ -3684,7 +3831,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C13" s="8" t="s">
-        <v>33</v>
+        <v>512</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>301</v>
@@ -3695,7 +3842,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C14" s="8" t="s">
-        <v>34</v>
+        <v>513</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>302</v>
@@ -3706,7 +3853,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C15" s="8" t="s">
-        <v>35</v>
+        <v>514</v>
       </c>
       <c r="D15" s="7" t="s">
         <v>223</v>
@@ -3717,7 +3864,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C16" s="8" t="s">
-        <v>36</v>
+        <v>515</v>
       </c>
       <c r="D16" s="7" t="s">
         <v>303</v>
@@ -3728,7 +3875,7 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C17" s="8" t="s">
-        <v>37</v>
+        <v>516</v>
       </c>
       <c r="D17" s="7" t="s">
         <v>304</v>
@@ -3736,7 +3883,7 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C18" s="8" t="s">
-        <v>38</v>
+        <v>517</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>305</v>
@@ -3744,7 +3891,7 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C19" s="8" t="s">
-        <v>39</v>
+        <v>518</v>
       </c>
       <c r="D19" s="7" t="s">
         <v>306</v>
@@ -3752,7 +3899,7 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C20" s="8" t="s">
-        <v>40</v>
+        <v>519</v>
       </c>
       <c r="D20" s="7" t="s">
         <v>307</v>
@@ -4087,7 +4234,7 @@
         <v>30</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>31</v>
+        <v>481</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>421</v>
@@ -4095,7 +4242,7 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C14" s="3" t="s">
-        <v>32</v>
+        <v>482</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>422</v>
@@ -4103,7 +4250,7 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C15" s="3" t="s">
-        <v>33</v>
+        <v>483</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>423</v>
@@ -4111,7 +4258,7 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C16" s="3" t="s">
-        <v>34</v>
+        <v>484</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>424</v>
@@ -4119,7 +4266,7 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C17" s="3" t="s">
-        <v>35</v>
+        <v>485</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>425</v>
@@ -4127,7 +4274,7 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C18" s="3" t="s">
-        <v>36</v>
+        <v>486</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>426</v>
@@ -4135,7 +4282,7 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C19" s="3" t="s">
-        <v>37</v>
+        <v>487</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>427</v>
@@ -4143,7 +4290,7 @@
     </row>
     <row r="20" spans="1:9" ht="24" x14ac:dyDescent="0.25">
       <c r="C20" s="3" t="s">
-        <v>38</v>
+        <v>488</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>428</v>
@@ -4157,7 +4304,7 @@
         <v>44</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>39</v>
+        <v>489</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>429</v>
@@ -4165,7 +4312,7 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C22" s="3" t="s">
-        <v>40</v>
+        <v>490</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>430</v>
@@ -4611,7 +4758,7 @@
         <v>30</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>31</v>
+        <v>500</v>
       </c>
       <c r="D10" s="12" t="s">
         <v>234</v>
@@ -4619,7 +4766,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C11" s="8" t="s">
-        <v>32</v>
+        <v>501</v>
       </c>
       <c r="D11" s="12" t="s">
         <v>236</v>
@@ -4630,7 +4777,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C12" s="8" t="s">
-        <v>33</v>
+        <v>502</v>
       </c>
       <c r="D12" s="12" t="s">
         <v>235</v>
@@ -4638,7 +4785,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C13" s="8" t="s">
-        <v>34</v>
+        <v>503</v>
       </c>
       <c r="D13" s="12" t="s">
         <v>237</v>
@@ -4649,7 +4796,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C14" s="8" t="s">
-        <v>35</v>
+        <v>504</v>
       </c>
       <c r="D14" s="12" t="s">
         <v>238</v>
@@ -4657,7 +4804,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C15" s="8" t="s">
-        <v>36</v>
+        <v>505</v>
       </c>
       <c r="D15" s="12" t="s">
         <v>239</v>
@@ -4668,7 +4815,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C16" s="8" t="s">
-        <v>37</v>
+        <v>506</v>
       </c>
       <c r="D16" s="12" t="s">
         <v>240</v>
@@ -4677,7 +4824,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C17" s="8" t="s">
-        <v>38</v>
+        <v>507</v>
       </c>
       <c r="D17" s="12" t="s">
         <v>241</v>
@@ -4688,7 +4835,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C18" s="8" t="s">
-        <v>39</v>
+        <v>508</v>
       </c>
       <c r="D18" s="12" t="s">
         <v>242</v>
@@ -4699,7 +4846,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C19" s="8" t="s">
-        <v>40</v>
+        <v>509</v>
       </c>
       <c r="D19" s="12" t="s">
         <v>243</v>
@@ -4867,7 +5014,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C10" s="8" t="s">
-        <v>32</v>
+        <v>491</v>
       </c>
       <c r="D10" s="11" t="s">
         <v>227</v>
@@ -4875,7 +5022,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C11" s="8" t="s">
-        <v>33</v>
+        <v>492</v>
       </c>
       <c r="D11" s="11" t="s">
         <v>339</v>
@@ -4884,7 +5031,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C12" s="8" t="s">
-        <v>34</v>
+        <v>493</v>
       </c>
       <c r="D12" s="11" t="s">
         <v>338</v>
@@ -4893,7 +5040,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C13" s="8" t="s">
-        <v>35</v>
+        <v>494</v>
       </c>
       <c r="D13" s="11" t="s">
         <v>228</v>
@@ -4901,7 +5048,7 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C14" s="8" t="s">
-        <v>36</v>
+        <v>495</v>
       </c>
       <c r="D14" s="11" t="s">
         <v>229</v>
@@ -4910,7 +5057,7 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C15" s="8" t="s">
-        <v>37</v>
+        <v>496</v>
       </c>
       <c r="D15" s="11" t="s">
         <v>230</v>
@@ -4919,7 +5066,7 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C16" s="8" t="s">
-        <v>38</v>
+        <v>497</v>
       </c>
       <c r="D16" s="11" t="s">
         <v>231</v>
@@ -4928,7 +5075,7 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C17" s="8" t="s">
-        <v>39</v>
+        <v>498</v>
       </c>
       <c r="D17" s="11" t="s">
         <v>232</v>
@@ -4937,7 +5084,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C18" s="8" t="s">
-        <v>40</v>
+        <v>499</v>
       </c>
       <c r="D18" s="11" t="s">
         <v>233</v>
@@ -6071,7 +6218,7 @@
         <v>30</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>31</v>
+        <v>471</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>352</v>
@@ -6079,7 +6226,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C13" s="3" t="s">
-        <v>32</v>
+        <v>472</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>353</v>
@@ -6087,7 +6234,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C14" s="3" t="s">
-        <v>33</v>
+        <v>473</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>354</v>
@@ -6095,7 +6242,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C15" s="3" t="s">
-        <v>34</v>
+        <v>474</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>355</v>
@@ -6103,7 +6250,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C16" s="3" t="s">
-        <v>35</v>
+        <v>475</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>356</v>
@@ -6111,7 +6258,7 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C17" s="3" t="s">
-        <v>36</v>
+        <v>476</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>357</v>
@@ -6119,7 +6266,7 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C18" s="3" t="s">
-        <v>37</v>
+        <v>477</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>358</v>
@@ -6127,7 +6274,7 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C19" s="3" t="s">
-        <v>38</v>
+        <v>478</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>359</v>
@@ -6138,7 +6285,7 @@
         <v>44</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>39</v>
+        <v>479</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>360</v>
@@ -6146,7 +6293,7 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C21" s="3" t="s">
-        <v>40</v>
+        <v>480</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>361</v>
